--- a/academias/Humanidades - Estadisticos 20211.xlsx
+++ b/academias/Humanidades - Estadisticos 20211.xlsx
@@ -622,25 +622,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>38.89</v>
+        <v>58.33</v>
       </c>
       <c r="H4">
-        <v>61.11</v>
+        <v>41.67</v>
       </c>
       <c r="I4">
-        <v>8.9</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>61.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -657,25 +657,25 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>74.36</v>
+        <v>82.05</v>
       </c>
       <c r="H5">
-        <v>25.64</v>
+        <v>17.95</v>
       </c>
       <c r="I5">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>25.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -692,25 +692,25 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>33.33</v>
+        <v>54.17</v>
       </c>
       <c r="H6">
-        <v>66.67</v>
+        <v>45.83</v>
       </c>
       <c r="I6">
-        <v>8.9</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>66.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -727,25 +727,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>62.5</v>
+        <v>72.5</v>
       </c>
       <c r="H7">
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K7">
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -762,25 +762,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>70.45</v>
+        <v>79.55</v>
       </c>
       <c r="H8">
-        <v>29.55</v>
+        <v>20.45</v>
       </c>
       <c r="I8">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>29.55</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -797,25 +797,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="H9">
-        <v>13.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I9">
         <v>6.6</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>13.95</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -832,25 +832,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>75.86</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H10">
-        <v>24.14</v>
+        <v>17.24</v>
       </c>
       <c r="I10">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>24.14</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -867,25 +867,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>61.9</v>
+        <v>76.19</v>
       </c>
       <c r="H11">
-        <v>38.1</v>
+        <v>23.81</v>
       </c>
       <c r="I11">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>38.1</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -937,25 +937,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H13">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
       <c r="I13">
         <v>9.300000000000001</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1007,25 +1007,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>62.5</v>
+        <v>84.38</v>
       </c>
       <c r="H15">
-        <v>37.5</v>
+        <v>15.63</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>37.5</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1042,25 +1042,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>77.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H16">
-        <v>22.86</v>
+        <v>5.71</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>22.86</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1077,25 +1077,25 @@
         <v>34</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>70.59</v>
+        <v>79.41</v>
       </c>
       <c r="H17">
-        <v>29.41</v>
+        <v>20.59</v>
       </c>
       <c r="I17">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>29.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1112,25 +1112,25 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>58.06</v>
+        <v>64.52</v>
       </c>
       <c r="H18">
-        <v>41.94</v>
+        <v>35.48</v>
       </c>
       <c r="I18">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>41.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1147,25 +1147,25 @@
         <v>36</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F19">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G19">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H19">
-        <v>30.56</v>
+        <v>22.22</v>
       </c>
       <c r="I19">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1194,13 +1194,13 @@
         <v>39.53</v>
       </c>
       <c r="I20">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>39.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1217,25 +1217,25 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F21">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G21">
-        <v>62.79</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H21">
-        <v>37.21</v>
+        <v>20.93</v>
       </c>
       <c r="I21">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>37.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1252,25 +1252,25 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>79.17</v>
+        <v>87.5</v>
       </c>
       <c r="H22">
-        <v>20.83</v>
+        <v>12.5</v>
       </c>
       <c r="I22">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>20.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1287,25 +1287,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>86.11</v>
+        <v>88.89</v>
       </c>
       <c r="H23">
-        <v>13.89</v>
+        <v>11.11</v>
       </c>
       <c r="I23">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>13.89</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
@@ -1371,22 +1371,25 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>66.67</v>
+      </c>
+      <c r="I2">
+        <v>5.9</v>
       </c>
       <c r="J2">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1403,22 +1406,25 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>38.1</v>
+      </c>
+      <c r="I3">
+        <v>6.3</v>
       </c>
       <c r="J3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1435,22 +1441,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>55.56</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>44.44</v>
+      </c>
+      <c r="I4">
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1467,22 +1476,25 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.62</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>15.38</v>
+      </c>
+      <c r="I5">
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1499,22 +1511,25 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>45.83</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>54.17</v>
+      </c>
+      <c r="I6">
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1531,22 +1546,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>27.5</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1563,22 +1581,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I8">
+        <v>7.1</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1595,22 +1616,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F9">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>20.93</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1627,22 +1651,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>65.52</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>34.48</v>
+      </c>
+      <c r="I10">
+        <v>7.6</v>
       </c>
       <c r="J10">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1659,22 +1686,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>28.57</v>
+      </c>
+      <c r="I11">
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1691,22 +1721,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>41.94</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>58.06</v>
+      </c>
+      <c r="I12">
+        <v>9.199999999999999</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1723,22 +1756,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F13">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>42.86</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>57.14</v>
+      </c>
+      <c r="I13">
+        <v>9.1</v>
       </c>
       <c r="J13">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1755,22 +1791,25 @@
         <v>35</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>34.29</v>
+      </c>
+      <c r="I14">
+        <v>8.9</v>
       </c>
       <c r="J14">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1787,22 +1826,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I15">
+        <v>8.5</v>
       </c>
       <c r="J15">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1819,22 +1861,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>17.14</v>
+      </c>
+      <c r="I16">
+        <v>8.1</v>
       </c>
       <c r="J16">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1851,22 +1896,25 @@
         <v>34</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>79.41</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>20.59</v>
+      </c>
+      <c r="I17">
+        <v>7.5</v>
       </c>
       <c r="J17">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1883,22 +1931,25 @@
         <v>31</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>58.06</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>41.94</v>
+      </c>
+      <c r="I18">
+        <v>6.7</v>
       </c>
       <c r="J18">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1915,22 +1966,25 @@
         <v>36</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>72.22</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>27.78</v>
+      </c>
+      <c r="I19">
+        <v>7.5</v>
       </c>
       <c r="J19">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1947,22 +2001,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>72.09</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>27.91</v>
+      </c>
+      <c r="I20">
+        <v>7.3</v>
       </c>
       <c r="J20">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1979,22 +2036,25 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>23.26</v>
+      </c>
+      <c r="I21">
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2011,22 +2071,25 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I22">
+        <v>7.3</v>
       </c>
       <c r="J22">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2043,22 +2106,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F23">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I23">
+        <v>6.9</v>
       </c>
       <c r="J23">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
@@ -2124,19 +2190,19 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>42.42</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>57.58</v>
+        <v>66.67</v>
       </c>
       <c r="I2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2171,7 +2237,7 @@
         <v>38.1</v>
       </c>
       <c r="I3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2194,25 +2260,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>38.89</v>
+        <v>55.56</v>
       </c>
       <c r="H4">
-        <v>61.11</v>
+        <v>44.44</v>
       </c>
       <c r="I4">
-        <v>8.9</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>61.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2229,25 +2295,25 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H5">
-        <v>25.64</v>
+        <v>15.38</v>
       </c>
       <c r="I5">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>25.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2264,25 +2330,25 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>33.33</v>
+        <v>45.83</v>
       </c>
       <c r="H6">
-        <v>66.67</v>
+        <v>54.17</v>
       </c>
       <c r="I6">
-        <v>8.9</v>
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>66.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2299,25 +2365,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>62.5</v>
+        <v>72.5</v>
       </c>
       <c r="H7">
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K7">
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2334,25 +2400,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>70.45</v>
+        <v>79.55</v>
       </c>
       <c r="H8">
-        <v>29.55</v>
+        <v>20.45</v>
       </c>
       <c r="I8">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>29.55</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2369,25 +2435,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>86.05</v>
+        <v>90.7</v>
       </c>
       <c r="H9">
-        <v>13.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I9">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>13.95</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2404,25 +2470,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>75.86</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H10">
-        <v>24.14</v>
+        <v>17.24</v>
       </c>
       <c r="I10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>24.14</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2439,25 +2505,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>61.9</v>
+        <v>76.19</v>
       </c>
       <c r="H11">
-        <v>38.1</v>
+        <v>23.81</v>
       </c>
       <c r="I11">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>38.1</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2486,7 +2552,7 @@
         <v>35.48</v>
       </c>
       <c r="I12">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>11</v>
@@ -2509,25 +2575,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="H13">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
       <c r="I13">
         <v>9.300000000000001</v>
       </c>
       <c r="J13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2556,7 +2622,7 @@
         <v>25.71</v>
       </c>
       <c r="I14">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -2579,25 +2645,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G15">
-        <v>62.5</v>
+        <v>84.38</v>
       </c>
       <c r="H15">
-        <v>37.5</v>
+        <v>15.63</v>
       </c>
       <c r="I15">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K15">
-        <v>37.5</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2614,25 +2680,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G16">
-        <v>77.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H16">
-        <v>22.86</v>
+        <v>5.71</v>
       </c>
       <c r="I16">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="J16">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K16">
-        <v>22.86</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2649,25 +2715,25 @@
         <v>34</v>
       </c>
       <c r="E17">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G17">
-        <v>70.59</v>
+        <v>79.41</v>
       </c>
       <c r="H17">
-        <v>29.41</v>
+        <v>20.59</v>
       </c>
       <c r="I17">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>29.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2696,13 +2762,13 @@
         <v>41.94</v>
       </c>
       <c r="I18">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K18">
-        <v>41.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2719,25 +2785,25 @@
         <v>36</v>
       </c>
       <c r="E19">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>69.44</v>
+        <v>72.22</v>
       </c>
       <c r="H19">
-        <v>30.56</v>
+        <v>27.78</v>
       </c>
       <c r="I19">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2754,25 +2820,25 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G20">
-        <v>60.47</v>
+        <v>72.09</v>
       </c>
       <c r="H20">
-        <v>39.53</v>
+        <v>27.91</v>
       </c>
       <c r="I20">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>39.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2789,25 +2855,25 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>62.79</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="H21">
-        <v>37.21</v>
+        <v>23.26</v>
       </c>
       <c r="I21">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>37.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2824,25 +2890,25 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>79.17</v>
+        <v>83.33</v>
       </c>
       <c r="H22">
-        <v>20.83</v>
+        <v>16.67</v>
       </c>
       <c r="I22">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>20.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2859,25 +2925,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G23">
-        <v>86.11</v>
+        <v>75</v>
       </c>
       <c r="H23">
-        <v>13.89</v>
+        <v>25</v>
       </c>
       <c r="I23">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <v>13.89</v>
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Humanidades - Estadisticos 20211.xlsx
+++ b/academias/Humanidades - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -145,6 +145,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -197,8 +201,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -499,42 +505,45 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -557,19 +566,19 @@
       <c r="F2">
         <v>19</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>42.42</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>57.58</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6.2</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -592,19 +601,19 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>61.9</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>38.1</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>7.2</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -627,19 +636,19 @@
       <c r="F4">
         <v>15</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>58.33</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>41.67</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.8</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -662,19 +671,19 @@
       <c r="F5">
         <v>7</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>82.05</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>17.95</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -697,19 +706,19 @@
       <c r="F6">
         <v>11</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>54.17</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>45.83</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>6.8</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -732,19 +741,19 @@
       <c r="F7">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>72.5</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>27.5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>6.5</v>
       </c>
       <c r="J7">
         <v>11</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>27.5</v>
       </c>
     </row>
@@ -767,19 +776,19 @@
       <c r="F8">
         <v>9</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>79.55</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>20.45</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>6.7</v>
       </c>
       <c r="J8">
         <v>9</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>20.45</v>
       </c>
     </row>
@@ -802,19 +811,19 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>90.7</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>9.300000000000001</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.6</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -837,19 +846,19 @@
       <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>82.76000000000001</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>17.24</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.1</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>17.24</v>
       </c>
     </row>
@@ -872,19 +881,19 @@
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>76.19</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>23.81</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>6.9</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>23.81</v>
       </c>
     </row>
@@ -907,19 +916,19 @@
       <c r="F12">
         <v>11</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>64.52</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>35.48</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.5</v>
       </c>
       <c r="J12">
         <v>11</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>35.48</v>
       </c>
     </row>
@@ -942,19 +951,19 @@
       <c r="F13">
         <v>9</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>57.14</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>42.86</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>42.86</v>
       </c>
     </row>
@@ -977,19 +986,19 @@
       <c r="F14">
         <v>9</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>74.29000000000001</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>25.71</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>8.5</v>
       </c>
       <c r="J14">
         <v>9</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>25.71</v>
       </c>
     </row>
@@ -1012,19 +1021,19 @@
       <c r="F15">
         <v>5</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>84.38</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>15.63</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>9.800000000000001</v>
       </c>
       <c r="J15">
         <v>5</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>15.63</v>
       </c>
     </row>
@@ -1047,19 +1056,19 @@
       <c r="F16">
         <v>2</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>94.29000000000001</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>5.71</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>9.699999999999999</v>
       </c>
       <c r="J16">
         <v>2</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>5.71</v>
       </c>
     </row>
@@ -1082,19 +1091,19 @@
       <c r="F17">
         <v>7</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>79.41</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>20.59</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>7.1</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1117,19 +1126,19 @@
       <c r="F18">
         <v>11</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>64.52</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>35.48</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>6.4</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1152,19 +1161,19 @@
       <c r="F19">
         <v>8</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>77.78</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>22.22</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>7.7</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1187,19 +1196,19 @@
       <c r="F20">
         <v>17</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>60.47</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>39.53</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>6.4</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1222,19 +1231,19 @@
       <c r="F21">
         <v>9</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>79.06999999999999</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>20.93</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>6.8</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1257,19 +1266,19 @@
       <c r="F22">
         <v>3</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>87.5</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>12.5</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>7.3</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1292,19 +1301,19 @@
       <c r="F23">
         <v>4</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>88.89</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>11.11</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>7.8</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>2.78</v>
       </c>
     </row>
@@ -1318,42 +1327,45 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1376,19 +1388,19 @@
       <c r="F2">
         <v>22</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>33.33</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>66.67</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>5.9</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>3.03</v>
       </c>
     </row>
@@ -1411,19 +1423,19 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>61.9</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>38.1</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>6.3</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1446,19 +1458,19 @@
       <c r="F4">
         <v>16</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>55.56</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>44.44</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1481,19 +1493,19 @@
       <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>84.62</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>15.38</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1516,19 +1528,19 @@
       <c r="F6">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>45.83</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>54.17</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>6.6</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1551,19 +1563,19 @@
       <c r="F7">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>72.5</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>27.5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7</v>
       </c>
       <c r="J7">
         <v>11</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>27.5</v>
       </c>
     </row>
@@ -1586,19 +1598,19 @@
       <c r="F8">
         <v>10</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>77.27</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>22.73</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.1</v>
       </c>
       <c r="J8">
         <v>10</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>22.73</v>
       </c>
     </row>
@@ -1621,19 +1633,19 @@
       <c r="F9">
         <v>9</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>79.06999999999999</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>20.93</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7</v>
       </c>
       <c r="J9">
         <v>9</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>20.93</v>
       </c>
     </row>
@@ -1656,19 +1668,19 @@
       <c r="F10">
         <v>10</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>65.52</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>34.48</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.6</v>
       </c>
       <c r="J10">
         <v>10</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>34.48</v>
       </c>
     </row>
@@ -1691,19 +1703,19 @@
       <c r="F11">
         <v>6</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>71.43000000000001</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>28.57</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.9</v>
       </c>
       <c r="J11">
         <v>6</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>28.57</v>
       </c>
     </row>
@@ -1726,19 +1738,19 @@
       <c r="F12">
         <v>18</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>41.94</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>58.06</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J12">
         <v>18</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>58.06</v>
       </c>
     </row>
@@ -1761,19 +1773,19 @@
       <c r="F13">
         <v>12</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>42.86</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>57.14</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>9.1</v>
       </c>
       <c r="J13">
         <v>12</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>57.14</v>
       </c>
     </row>
@@ -1796,19 +1808,19 @@
       <c r="F14">
         <v>12</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>65.70999999999999</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>34.29</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>8.9</v>
       </c>
       <c r="J14">
         <v>12</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>34.29</v>
       </c>
     </row>
@@ -1831,19 +1843,19 @@
       <c r="F15">
         <v>8</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>75</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>25</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>8.5</v>
       </c>
       <c r="J15">
         <v>8</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>25</v>
       </c>
     </row>
@@ -1866,19 +1878,19 @@
       <c r="F16">
         <v>6</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>82.86</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>17.14</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>8.1</v>
       </c>
       <c r="J16">
         <v>6</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>17.14</v>
       </c>
     </row>
@@ -1901,19 +1913,19 @@
       <c r="F17">
         <v>7</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>79.41</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>20.59</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>7.5</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1936,19 +1948,19 @@
       <c r="F18">
         <v>13</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>58.06</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>41.94</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>6.7</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1971,19 +1983,19 @@
       <c r="F19">
         <v>10</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>72.22</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>27.78</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>7.5</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2006,19 +2018,19 @@
       <c r="F20">
         <v>12</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>72.09</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>27.91</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>7.3</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2041,19 +2053,19 @@
       <c r="F21">
         <v>10</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>76.73999999999999</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>23.26</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>7</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2076,19 +2088,19 @@
       <c r="F22">
         <v>4</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>83.33</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>16.67</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>7.3</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2111,19 +2123,19 @@
       <c r="F23">
         <v>9</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>75</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>25</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>6.9</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>2.78</v>
       </c>
     </row>
@@ -2137,42 +2149,45 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2195,19 +2210,19 @@
       <c r="F2">
         <v>22</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>33.33</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>66.67</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6.1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2230,19 +2245,19 @@
       <c r="F3">
         <v>8</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>61.9</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>38.1</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>6.9</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2265,19 +2280,19 @@
       <c r="F4">
         <v>16</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>55.56</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>44.44</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2300,19 +2315,19 @@
       <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>84.62</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>15.38</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2335,19 +2350,19 @@
       <c r="F6">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>45.83</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>54.17</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>6.8</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2370,19 +2385,19 @@
       <c r="F7">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>72.5</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>27.5</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>6.9</v>
       </c>
       <c r="J7">
         <v>11</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>27.5</v>
       </c>
     </row>
@@ -2405,19 +2420,19 @@
       <c r="F8">
         <v>9</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>79.55</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>20.45</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.1</v>
       </c>
       <c r="J8">
         <v>9</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>20.45</v>
       </c>
     </row>
@@ -2440,19 +2455,19 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>90.7</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>9.300000000000001</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.9</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -2475,19 +2490,19 @@
       <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>82.76000000000001</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>17.24</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.4</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>17.24</v>
       </c>
     </row>
@@ -2510,19 +2525,19 @@
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>76.19</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>23.81</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.5</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>23.81</v>
       </c>
     </row>
@@ -2545,19 +2560,19 @@
       <c r="F12">
         <v>11</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>64.52</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>35.48</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.6</v>
       </c>
       <c r="J12">
         <v>11</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>35.48</v>
       </c>
     </row>
@@ -2580,19 +2595,19 @@
       <c r="F13">
         <v>9</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>57.14</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>42.86</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>42.86</v>
       </c>
     </row>
@@ -2615,19 +2630,19 @@
       <c r="F14">
         <v>9</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>74.29000000000001</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>25.71</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>8.9</v>
       </c>
       <c r="J14">
         <v>9</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>25.71</v>
       </c>
     </row>
@@ -2650,19 +2665,19 @@
       <c r="F15">
         <v>5</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>84.38</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>15.63</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>9.5</v>
       </c>
       <c r="J15">
         <v>5</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>15.63</v>
       </c>
     </row>
@@ -2685,19 +2700,19 @@
       <c r="F16">
         <v>2</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>94.29000000000001</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>5.71</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>9.1</v>
       </c>
       <c r="J16">
         <v>2</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>5.71</v>
       </c>
     </row>
@@ -2720,19 +2735,19 @@
       <c r="F17">
         <v>7</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>79.41</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>20.59</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>7.4</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2755,19 +2770,19 @@
       <c r="F18">
         <v>13</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>58.06</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>41.94</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>6.6</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2790,19 +2805,19 @@
       <c r="F19">
         <v>10</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>72.22</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>27.78</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>7.8</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2825,19 +2840,19 @@
       <c r="F20">
         <v>12</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>72.09</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>27.91</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>7</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2860,19 +2875,19 @@
       <c r="F21">
         <v>10</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>76.73999999999999</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>23.26</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>7.1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2895,19 +2910,19 @@
       <c r="F22">
         <v>4</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>83.33</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>16.67</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>7.4</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2930,19 +2945,19 @@
       <c r="F23">
         <v>9</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>75</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>25</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>7.5</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>2.78</v>
       </c>
     </row>

--- a/academias/Humanidades - Estadisticos 20211.xlsx
+++ b/academias/Humanidades - Estadisticos 20211.xlsx
@@ -146,7 +146,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Humanidades - Estadisticos 20211.xlsx
+++ b/academias/Humanidades - Estadisticos 20211.xlsx
@@ -1016,25 +1016,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H15" s="1">
-        <v>15.63</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I15" s="2">
         <v>9.800000000000001</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1">
-        <v>15.63</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1838,25 +1838,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>75</v>
+        <v>84.38</v>
       </c>
       <c r="H15" s="1">
-        <v>25</v>
+        <v>15.63</v>
       </c>
       <c r="I15" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K15" s="1">
-        <v>25</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2660,25 +2660,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" s="1">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H15" s="1">
-        <v>15.63</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I15" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K15" s="1">
-        <v>15.63</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:11">

--- a/academias/Humanidades - Estadisticos 20211.xlsx
+++ b/academias/Humanidades - Estadisticos 20211.xlsx
@@ -736,25 +736,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="H7" s="1">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="I7" s="2">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -771,25 +771,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>79.55</v>
+        <v>86.36</v>
       </c>
       <c r="H8" s="1">
-        <v>20.45</v>
+        <v>13.64</v>
       </c>
       <c r="I8" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>20.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -806,25 +806,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>90.7</v>
+        <v>93.02</v>
       </c>
       <c r="H9" s="1">
-        <v>9.300000000000001</v>
+        <v>6.98</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -841,25 +841,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>82.76000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="H10" s="1">
-        <v>17.24</v>
+        <v>10.34</v>
       </c>
       <c r="I10" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>17.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -876,25 +876,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H11" s="1">
-        <v>23.81</v>
+        <v>19.05</v>
       </c>
       <c r="I11" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -911,25 +911,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>64.52</v>
+        <v>74.19</v>
       </c>
       <c r="H12" s="1">
-        <v>35.48</v>
+        <v>25.81</v>
       </c>
       <c r="I12" s="2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -946,25 +946,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="I13" s="2">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -981,25 +981,25 @@
         <v>35</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>74.29000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="H14" s="1">
-        <v>25.71</v>
+        <v>17.14</v>
       </c>
       <c r="I14" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>25.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1016,25 +1016,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1051,25 +1051,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1118,19 +1118,19 @@
         <v>40</v>
       </c>
       <c r="D18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18">
         <v>20</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="1">
-        <v>64.52</v>
+        <v>62.5</v>
       </c>
       <c r="H18" s="1">
-        <v>35.48</v>
+        <v>37.5</v>
       </c>
       <c r="I18" s="2">
         <v>6.4</v>
@@ -1311,10 +1311,10 @@
         <v>7.8</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1398,10 +1398,10 @@
         <v>5.9</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="H7" s="1">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1593,25 +1593,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>77.27</v>
+        <v>86.36</v>
       </c>
       <c r="H8" s="1">
-        <v>22.73</v>
+        <v>13.64</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1628,25 +1628,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>79.06999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="H9" s="1">
-        <v>20.93</v>
+        <v>11.63</v>
       </c>
       <c r="I9" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>20.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1663,25 +1663,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>65.52</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>34.48</v>
+        <v>13.79</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>34.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1698,25 +1698,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>71.43000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="H11" s="1">
-        <v>28.57</v>
+        <v>19.05</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1733,25 +1733,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>41.94</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>58.06</v>
+        <v>32.26</v>
       </c>
       <c r="I12" s="2">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>58.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1768,25 +1768,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>42.86</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>57.14</v>
+        <v>33.33</v>
       </c>
       <c r="I13" s="2">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>57.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1803,25 +1803,25 @@
         <v>35</v>
       </c>
       <c r="E14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>65.70999999999999</v>
+        <v>82.86</v>
       </c>
       <c r="H14" s="1">
-        <v>34.29</v>
+        <v>17.14</v>
       </c>
       <c r="I14" s="2">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>34.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1838,25 +1838,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1873,25 +1873,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>82.86</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>17.14</v>
+        <v>5.71</v>
       </c>
       <c r="I16" s="2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>17.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1940,22 +1940,22 @@
         <v>40</v>
       </c>
       <c r="D18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18">
         <v>18</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1">
-        <v>58.06</v>
+        <v>56.25</v>
       </c>
       <c r="H18" s="1">
-        <v>41.94</v>
+        <v>43.75</v>
       </c>
       <c r="I18" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>6.9</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2205,19 +2205,19 @@
         <v>33</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>33.33</v>
+        <v>63.64</v>
       </c>
       <c r="H2" s="1">
-        <v>66.67</v>
+        <v>36.36</v>
       </c>
       <c r="I2" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2240,19 +2240,19 @@
         <v>21</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>61.9</v>
+        <v>66.67</v>
       </c>
       <c r="H3" s="1">
-        <v>38.1</v>
+        <v>33.33</v>
       </c>
       <c r="I3" s="2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2275,19 +2275,19 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1">
-        <v>55.56</v>
+        <v>58.33</v>
       </c>
       <c r="H4" s="1">
-        <v>44.44</v>
+        <v>41.67</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2310,19 +2310,19 @@
         <v>39</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>84.62</v>
+        <v>82.05</v>
       </c>
       <c r="H5" s="1">
-        <v>15.38</v>
+        <v>17.95</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2345,19 +2345,19 @@
         <v>24</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>45.83</v>
+        <v>66.67</v>
       </c>
       <c r="H6" s="1">
-        <v>54.17</v>
+        <v>33.33</v>
       </c>
       <c r="I6" s="2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2380,25 +2380,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>72.5</v>
+        <v>67.5</v>
       </c>
       <c r="H7" s="1">
-        <v>27.5</v>
+        <v>32.5</v>
       </c>
       <c r="I7" s="2">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2415,25 +2415,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>79.55</v>
+        <v>86.36</v>
       </c>
       <c r="H8" s="1">
-        <v>20.45</v>
+        <v>13.64</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>20.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2450,25 +2450,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>90.7</v>
+        <v>88.37</v>
       </c>
       <c r="H9" s="1">
-        <v>9.300000000000001</v>
+        <v>11.63</v>
       </c>
       <c r="I9" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2485,25 +2485,25 @@
         <v>29</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>17.24</v>
+        <v>13.79</v>
       </c>
       <c r="I10" s="2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>17.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2520,25 +2520,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>76.19</v>
+        <v>80.95</v>
       </c>
       <c r="H11" s="1">
-        <v>23.81</v>
+        <v>19.05</v>
       </c>
       <c r="I11" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>23.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2567,13 +2567,13 @@
         <v>35.48</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2590,25 +2590,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="H13" s="1">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
       <c r="I13" s="2">
-        <v>9.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2625,25 +2625,25 @@
         <v>35</v>
       </c>
       <c r="E14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G14" s="1">
-        <v>74.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>25.71</v>
+        <v>14.29</v>
       </c>
       <c r="I14" s="2">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="J14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>25.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2660,25 +2660,25 @@
         <v>32</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2695,25 +2695,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>94.29000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>5.71</v>
+        <v>8.57</v>
       </c>
       <c r="I16" s="2">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2730,19 +2730,19 @@
         <v>34</v>
       </c>
       <c r="E17">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>79.41</v>
+        <v>97.06</v>
       </c>
       <c r="H17" s="1">
-        <v>20.59</v>
+        <v>2.94</v>
       </c>
       <c r="I17" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2762,22 +2762,22 @@
         <v>40</v>
       </c>
       <c r="D18">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E18">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>58.06</v>
+        <v>75</v>
       </c>
       <c r="H18" s="1">
-        <v>41.94</v>
+        <v>25</v>
       </c>
       <c r="I18" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2800,19 +2800,19 @@
         <v>36</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1">
-        <v>72.22</v>
+        <v>80.56</v>
       </c>
       <c r="H19" s="1">
-        <v>27.78</v>
+        <v>19.44</v>
       </c>
       <c r="I19" s="2">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2835,19 +2835,19 @@
         <v>43</v>
       </c>
       <c r="E20">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F20">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1">
-        <v>72.09</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>27.91</v>
+        <v>18.6</v>
       </c>
       <c r="I20" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2870,19 +2870,19 @@
         <v>43</v>
       </c>
       <c r="E21">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" s="1">
-        <v>76.73999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>23.26</v>
+        <v>20.93</v>
       </c>
       <c r="I21" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2905,19 +2905,19 @@
         <v>24</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H22" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
       <c r="I22" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2940,25 +2940,25 @@
         <v>36</v>
       </c>
       <c r="E23">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1">
-        <v>75</v>
+        <v>80.56</v>
       </c>
       <c r="H23" s="1">
-        <v>25</v>
+        <v>19.44</v>
       </c>
       <c r="I23" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Humanidades - Estadisticos 20211.xlsx
+++ b/academias/Humanidades - Estadisticos 20211.xlsx
@@ -2695,16 +2695,16 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="I16" s="2">
         <v>8</v>
